--- a/locale/translations.xlsx
+++ b/locale/translations.xlsx
@@ -850,11 +850,19 @@
           <t>Chain of custody</t>
         </is>
       </c>
-      <c r="B15" s="3" t="inlineStr"/>
-      <c r="C15" s="3" t="inlineStr"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>Chain of custody</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>Chain of custody</t>
+        </is>
+      </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>Blank: please supply</t>
+          <t>English placeholder: please translate</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -1038,11 +1046,19 @@
           <t>Biomass Mitra</t>
         </is>
       </c>
-      <c r="B22" s="3" t="inlineStr"/>
-      <c r="C22" s="3" t="inlineStr"/>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>Biomass Mitra</t>
+        </is>
+      </c>
+      <c r="C22" s="3" t="inlineStr">
+        <is>
+          <t>Biomass Mitra</t>
+        </is>
+      </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>Blank: please supply</t>
+          <t>English placeholder: please translate</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -1590,11 +1606,19 @@
           <t>Tamper-evident trail</t>
         </is>
       </c>
-      <c r="B42" s="3" t="inlineStr"/>
-      <c r="C42" s="3" t="inlineStr"/>
+      <c r="B42" s="3" t="inlineStr">
+        <is>
+          <t>Tamper-evident trail</t>
+        </is>
+      </c>
+      <c r="C42" s="3" t="inlineStr">
+        <is>
+          <t>Tamper-evident trail</t>
+        </is>
+      </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>Blank: please supply</t>
+          <t>English placeholder: please translate</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
@@ -1610,11 +1634,19 @@
           <t>Each entry carries a fingerprint of the one before it, so a changed record would be detected.</t>
         </is>
       </c>
-      <c r="B43" s="3" t="inlineStr"/>
-      <c r="C43" s="3" t="inlineStr"/>
+      <c r="B43" s="3" t="inlineStr">
+        <is>
+          <t>Each entry carries a fingerprint of the one before it, so a changed record would be detected.</t>
+        </is>
+      </c>
+      <c r="C43" s="3" t="inlineStr">
+        <is>
+          <t>Each entry carries a fingerprint of the one before it, so a changed record would be detected.</t>
+        </is>
+      </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>Blank: please supply</t>
+          <t>English placeholder: please translate</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
@@ -1658,11 +1690,19 @@
           <t>Farmers: %(n)s. Shared out by what each handed over at the Grid. Codes and villages only.</t>
         </is>
       </c>
-      <c r="B45" s="3" t="inlineStr"/>
-      <c r="C45" s="3" t="inlineStr"/>
+      <c r="B45" s="3" t="inlineStr">
+        <is>
+          <t>Farmers: %(n)s. Shared out by what each handed over at the Grid. Codes and villages only.</t>
+        </is>
+      </c>
+      <c r="C45" s="3" t="inlineStr">
+        <is>
+          <t>Farmers: %(n)s. Shared out by what each handed over at the Grid. Codes and villages only.</t>
+        </is>
+      </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>Blank: please supply</t>
+          <t>English placeholder: please translate</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
@@ -2854,11 +2894,19 @@
           <t>Book inventory</t>
         </is>
       </c>
-      <c r="B88" s="3" t="inlineStr"/>
-      <c r="C88" s="3" t="inlineStr"/>
+      <c r="B88" s="3" t="inlineStr">
+        <is>
+          <t>Book inventory</t>
+        </is>
+      </c>
+      <c r="C88" s="3" t="inlineStr">
+        <is>
+          <t>Book inventory</t>
+        </is>
+      </c>
       <c r="D88" s="2" t="inlineStr">
         <is>
-          <t>Blank: please supply</t>
+          <t>English placeholder: please translate</t>
         </is>
       </c>
       <c r="E88" s="2" t="inlineStr">
@@ -2902,11 +2950,19 @@
           <t>Physical inventory</t>
         </is>
       </c>
-      <c r="B90" s="3" t="inlineStr"/>
-      <c r="C90" s="3" t="inlineStr"/>
+      <c r="B90" s="3" t="inlineStr">
+        <is>
+          <t>Physical inventory</t>
+        </is>
+      </c>
+      <c r="C90" s="3" t="inlineStr">
+        <is>
+          <t>Physical inventory</t>
+        </is>
+      </c>
       <c r="D90" s="2" t="inlineStr">
         <is>
-          <t>Blank: please supply</t>
+          <t>English placeholder: please translate</t>
         </is>
       </c>
       <c r="E90" s="2" t="inlineStr">
@@ -2950,11 +3006,19 @@
           <t>Usable inventory</t>
         </is>
       </c>
-      <c r="B92" s="3" t="inlineStr"/>
-      <c r="C92" s="3" t="inlineStr"/>
+      <c r="B92" s="3" t="inlineStr">
+        <is>
+          <t>Usable inventory</t>
+        </is>
+      </c>
+      <c r="C92" s="3" t="inlineStr">
+        <is>
+          <t>Usable inventory</t>
+        </is>
+      </c>
       <c r="D92" s="2" t="inlineStr">
         <is>
-          <t>Blank: please supply</t>
+          <t>English placeholder: please translate</t>
         </is>
       </c>
       <c r="E92" s="2" t="inlineStr">
@@ -2998,11 +3062,19 @@
           <t>Fuel cover</t>
         </is>
       </c>
-      <c r="B94" s="3" t="inlineStr"/>
-      <c r="C94" s="3" t="inlineStr"/>
+      <c r="B94" s="3" t="inlineStr">
+        <is>
+          <t>Fuel cover</t>
+        </is>
+      </c>
+      <c r="C94" s="3" t="inlineStr">
+        <is>
+          <t>Fuel cover</t>
+        </is>
+      </c>
       <c r="D94" s="2" t="inlineStr">
         <is>
-          <t>Blank: please supply</t>
+          <t>English placeholder: please translate</t>
         </is>
       </c>
       <c r="E94" s="2" t="inlineStr">
@@ -3942,19 +4014,19 @@
           <t>%(d)s (%(pc)s%%)</t>
         </is>
       </c>
-      <c r="B128" s="2" t="inlineStr">
+      <c r="B128" s="3" t="inlineStr">
         <is>
           <t>%(d)s (%(pc)s%%)</t>
         </is>
       </c>
-      <c r="C128" s="2" t="inlineStr">
+      <c r="C128" s="3" t="inlineStr">
         <is>
           <t>%(d)s (%(pc)s%%)</t>
         </is>
       </c>
       <c r="D128" s="2" t="inlineStr">
         <is>
-          <t>Draft: please check</t>
+          <t>English placeholder: please translate</t>
         </is>
       </c>
       <c r="E128" s="2" t="inlineStr">
@@ -4082,11 +4154,19 @@
           <t>Biomass Mitras</t>
         </is>
       </c>
-      <c r="B133" s="3" t="inlineStr"/>
-      <c r="C133" s="3" t="inlineStr"/>
+      <c r="B133" s="3" t="inlineStr">
+        <is>
+          <t>Biomass Mitras</t>
+        </is>
+      </c>
+      <c r="C133" s="3" t="inlineStr">
+        <is>
+          <t>Biomass Mitras</t>
+        </is>
+      </c>
       <c r="D133" s="2" t="inlineStr">
         <is>
-          <t>Blank: please supply</t>
+          <t>English placeholder: please translate</t>
         </is>
       </c>
       <c r="E133" s="2" t="inlineStr">
@@ -4102,11 +4182,19 @@
           <t>No Mitra recorded.</t>
         </is>
       </c>
-      <c r="B134" s="3" t="inlineStr"/>
-      <c r="C134" s="3" t="inlineStr"/>
+      <c r="B134" s="3" t="inlineStr">
+        <is>
+          <t>No Mitra recorded.</t>
+        </is>
+      </c>
+      <c r="C134" s="3" t="inlineStr">
+        <is>
+          <t>No Mitra recorded.</t>
+        </is>
+      </c>
       <c r="D134" s="2" t="inlineStr">
         <is>
-          <t>Blank: please supply</t>
+          <t>English placeholder: please translate</t>
         </is>
       </c>
       <c r="E134" s="2" t="inlineStr">
@@ -4122,11 +4210,19 @@
           <t>Grids</t>
         </is>
       </c>
-      <c r="B135" s="3" t="inlineStr"/>
-      <c r="C135" s="3" t="inlineStr"/>
+      <c r="B135" s="3" t="inlineStr">
+        <is>
+          <t>Grids</t>
+        </is>
+      </c>
+      <c r="C135" s="3" t="inlineStr">
+        <is>
+          <t>Grids</t>
+        </is>
+      </c>
       <c r="D135" s="2" t="inlineStr">
         <is>
-          <t>Blank: please supply</t>
+          <t>English placeholder: please translate</t>
         </is>
       </c>
       <c r="E135" s="2" t="inlineStr">
@@ -4142,11 +4238,19 @@
           <t>Attributed</t>
         </is>
       </c>
-      <c r="B136" s="3" t="inlineStr"/>
-      <c r="C136" s="3" t="inlineStr"/>
+      <c r="B136" s="3" t="inlineStr">
+        <is>
+          <t>Attributed</t>
+        </is>
+      </c>
+      <c r="C136" s="3" t="inlineStr">
+        <is>
+          <t>Attributed</t>
+        </is>
+      </c>
       <c r="D136" s="2" t="inlineStr">
         <is>
-          <t>Blank: please supply</t>
+          <t>English placeholder: please translate</t>
         </is>
       </c>
       <c r="E136" s="2" t="inlineStr">
@@ -4190,11 +4294,19 @@
           <t>%(t)s delivered. Farmers are shared out in proportion to the tonnes each handed over at the supplying Grid (the lots are not tagged farmer by farmer), so read this as a fair attribution, not lot-level proof. Only farmer codes and villages are shown.</t>
         </is>
       </c>
-      <c r="B138" s="3" t="inlineStr"/>
-      <c r="C138" s="3" t="inlineStr"/>
+      <c r="B138" s="3" t="inlineStr">
+        <is>
+          <t>%(t)s delivered. Farmers are shared out in proportion to the tonnes each handed over at the supplying Grid (the lots are not tagged farmer by farmer), so read this as a fair attribution, not lot-level proof. Only farmer codes and villages are shown.</t>
+        </is>
+      </c>
+      <c r="C138" s="3" t="inlineStr">
+        <is>
+          <t>%(t)s delivered. Farmers are shared out in proportion to the tonnes each handed over at the supplying Grid (the lots are not tagged farmer by farmer), so read this as a fair attribution, not lot-level proof. Only farmer codes and villages are shown.</t>
+        </is>
+      </c>
       <c r="D138" s="2" t="inlineStr">
         <is>
-          <t>Blank: please supply</t>
+          <t>English placeholder: please translate</t>
         </is>
       </c>
       <c r="E138" s="2" t="inlineStr">
@@ -4238,11 +4350,19 @@
           <t>%(t)s could not be attributed because no farmer pickups are recorded for it.</t>
         </is>
       </c>
-      <c r="B140" s="3" t="inlineStr"/>
-      <c r="C140" s="3" t="inlineStr"/>
+      <c r="B140" s="3" t="inlineStr">
+        <is>
+          <t>%(t)s could not be attributed because no farmer pickups are recorded for it.</t>
+        </is>
+      </c>
+      <c r="C140" s="3" t="inlineStr">
+        <is>
+          <t>%(t)s could not be attributed because no farmer pickups are recorded for it.</t>
+        </is>
+      </c>
       <c r="D140" s="2" t="inlineStr">
         <is>
-          <t>Blank: please supply</t>
+          <t>English placeholder: please translate</t>
         </is>
       </c>
       <c r="E140" s="2" t="inlineStr">
@@ -4342,11 +4462,19 @@
           <t>Confidence</t>
         </is>
       </c>
-      <c r="B144" s="3" t="inlineStr"/>
-      <c r="C144" s="3" t="inlineStr"/>
+      <c r="B144" s="3" t="inlineStr">
+        <is>
+          <t>Confidence</t>
+        </is>
+      </c>
+      <c r="C144" s="3" t="inlineStr">
+        <is>
+          <t>Confidence</t>
+        </is>
+      </c>
       <c r="D144" s="2" t="inlineStr">
         <is>
-          <t>Blank: please supply</t>
+          <t>English placeholder: please translate</t>
         </is>
       </c>
       <c r="E144" s="2" t="inlineStr">
@@ -4558,11 +4686,19 @@
           <t>ESG / sustainability</t>
         </is>
       </c>
-      <c r="B152" s="3" t="inlineStr"/>
-      <c r="C152" s="3" t="inlineStr"/>
+      <c r="B152" s="3" t="inlineStr">
+        <is>
+          <t>ESG / sustainability</t>
+        </is>
+      </c>
+      <c r="C152" s="3" t="inlineStr">
+        <is>
+          <t>ESG / sustainability</t>
+        </is>
+      </c>
       <c r="D152" s="2" t="inlineStr">
         <is>
-          <t>Blank: please supply</t>
+          <t>English placeholder: please translate</t>
         </is>
       </c>
       <c r="E152" s="2" t="inlineStr">
@@ -4578,11 +4714,19 @@
           <t>Regenerix</t>
         </is>
       </c>
-      <c r="B153" s="3" t="inlineStr"/>
-      <c r="C153" s="3" t="inlineStr"/>
+      <c r="B153" s="3" t="inlineStr">
+        <is>
+          <t>Regenerix</t>
+        </is>
+      </c>
+      <c r="C153" s="3" t="inlineStr">
+        <is>
+          <t>Regenerix</t>
+        </is>
+      </c>
       <c r="D153" s="2" t="inlineStr">
         <is>
-          <t>Blank: please supply</t>
+          <t>English placeholder: please translate</t>
         </is>
       </c>
       <c r="E153" s="2" t="inlineStr">
@@ -4598,11 +4742,19 @@
           <t>VLE</t>
         </is>
       </c>
-      <c r="B154" s="3" t="inlineStr"/>
-      <c r="C154" s="3" t="inlineStr"/>
+      <c r="B154" s="3" t="inlineStr">
+        <is>
+          <t>VLE</t>
+        </is>
+      </c>
+      <c r="C154" s="3" t="inlineStr">
+        <is>
+          <t>VLE</t>
+        </is>
+      </c>
       <c r="D154" s="2" t="inlineStr">
         <is>
-          <t>Blank: please supply</t>
+          <t>English placeholder: please translate</t>
         </is>
       </c>
       <c r="E154" s="2" t="inlineStr">
@@ -5738,11 +5890,19 @@
           <t>Reconcile</t>
         </is>
       </c>
-      <c r="B195" s="3" t="inlineStr"/>
-      <c r="C195" s="3" t="inlineStr"/>
+      <c r="B195" s="3" t="inlineStr">
+        <is>
+          <t>Reconcile</t>
+        </is>
+      </c>
+      <c r="C195" s="3" t="inlineStr">
+        <is>
+          <t>Reconcile</t>
+        </is>
+      </c>
       <c r="D195" s="2" t="inlineStr">
         <is>
-          <t>Blank: please supply</t>
+          <t>English placeholder: please translate</t>
         </is>
       </c>
       <c r="E195" s="2" t="inlineStr">
@@ -5786,11 +5946,19 @@
           <t>Low fuel cover</t>
         </is>
       </c>
-      <c r="B197" s="3" t="inlineStr"/>
-      <c r="C197" s="3" t="inlineStr"/>
+      <c r="B197" s="3" t="inlineStr">
+        <is>
+          <t>Low fuel cover</t>
+        </is>
+      </c>
+      <c r="C197" s="3" t="inlineStr">
+        <is>
+          <t>Low fuel cover</t>
+        </is>
+      </c>
       <c r="D197" s="2" t="inlineStr">
         <is>
-          <t>Blank: please supply</t>
+          <t>English placeholder: please translate</t>
         </is>
       </c>
       <c r="E197" s="2" t="inlineStr">
@@ -5806,11 +5974,19 @@
           <t>%(days)s days of cover is less than the %(lead)s-day replenishment lead time.</t>
         </is>
       </c>
-      <c r="B198" s="3" t="inlineStr"/>
-      <c r="C198" s="3" t="inlineStr"/>
+      <c r="B198" s="3" t="inlineStr">
+        <is>
+          <t>%(days)s days of cover is less than the %(lead)s-day replenishment lead time.</t>
+        </is>
+      </c>
+      <c r="C198" s="3" t="inlineStr">
+        <is>
+          <t>%(days)s days of cover is less than the %(lead)s-day replenishment lead time.</t>
+        </is>
+      </c>
       <c r="D198" s="2" t="inlineStr">
         <is>
-          <t>Blank: please supply</t>
+          <t>English placeholder: please translate</t>
         </is>
       </c>
       <c r="E198" s="2" t="inlineStr">
@@ -6106,11 +6282,19 @@
           <t>At the Grid</t>
         </is>
       </c>
-      <c r="B209" s="3" t="inlineStr"/>
-      <c r="C209" s="3" t="inlineStr"/>
+      <c r="B209" s="3" t="inlineStr">
+        <is>
+          <t>At the Grid</t>
+        </is>
+      </c>
+      <c r="C209" s="3" t="inlineStr">
+        <is>
+          <t>At the Grid</t>
+        </is>
+      </c>
       <c r="D209" s="2" t="inlineStr">
         <is>
-          <t>Blank: please supply</t>
+          <t>English placeholder: please translate</t>
         </is>
       </c>
       <c r="E209" s="2" t="inlineStr">
@@ -6126,11 +6310,19 @@
           <t>At the Hub</t>
         </is>
       </c>
-      <c r="B210" s="3" t="inlineStr"/>
-      <c r="C210" s="3" t="inlineStr"/>
+      <c r="B210" s="3" t="inlineStr">
+        <is>
+          <t>At the Hub</t>
+        </is>
+      </c>
+      <c r="C210" s="3" t="inlineStr">
+        <is>
+          <t>At the Hub</t>
+        </is>
+      </c>
       <c r="D210" s="2" t="inlineStr">
         <is>
-          <t>Blank: please supply</t>
+          <t>English placeholder: please translate</t>
         </is>
       </c>
       <c r="E210" s="2" t="inlineStr">
@@ -6171,7 +6363,7 @@
   </sheetData>
   <dataValidations count="1">
     <dataValidation sqref="D2:D211" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"Blank: please supply,Draft: please check,Checked in the field,Needs discussion"</formula1>
+      <formula1>"English placeholder: please translate,Draft: please check,Checked in the field,Needs discussion"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6200,7 +6392,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Column A is the English. Fill in or correct column B (Hindi) and column C (Punjabi). Yellow cells are blank because I was not sure of the local wording.</t>
+          <t>Column A is the English. Fill in or correct column B (Hindi) and column C (Punjabi). Yellow cells still show the English word because I was not sure of the local wording; please replace it.</t>
         </is>
       </c>
     </row>
